--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2021_magallanes.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:27</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -698,19 +698,19 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12">
@@ -744,19 +744,19 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="13">
@@ -767,19 +767,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="14">
@@ -813,19 +813,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.12</v>
+        <v>0.75</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.11</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="16">
@@ -836,19 +836,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.72</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="17">
@@ -859,19 +859,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="18">
